--- a/src/attributions/attributions_ig_traj_156.xlsx
+++ b/src/attributions/attributions_ig_traj_156.xlsx
@@ -999,52 +999,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00422558526721888</v>
+        <v>0.02573828932966507</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001956043344497194</v>
+        <v>0.03867200513956757</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001516576875198152</v>
+        <v>0.01737741520217634</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.006383627946666925</v>
+        <v>-0.06816412673353098</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001766573290872586</v>
+        <v>-0.0738977701328799</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02345198358017451</v>
+        <v>0.2591336860416013</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-6.00842008908948e-13</v>
+        <v>-5.216696166763571e-11</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1065,40 +1065,40 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-5.908839353854478e-12</v>
+        <v>-4.156858820832936e-11</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.269638605781068e-12</v>
+        <v>-4.878510714229741e-11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.007816214840258033</v>
+        <v>-0.1375414841926664</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.002368183946210966</v>
+        <v>-0.01059594189404425</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002333183021126038</v>
+        <v>-0.07145661471681042</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
@@ -1110,19 +1110,19 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001298900273058594</v>
+        <v>-0.02178121979840222</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.005808898183108543</v>
+        <v>-0.0009704303764569326</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.004921308304145306</v>
+        <v>-0.08790985876720699</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0</v>
@@ -1134,76 +1134,76 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.01049347133087024</v>
+        <v>0.1751802514603586</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.006980732347296172</v>
+        <v>0.04831727053582048</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.01514477084622037</v>
+        <v>-0.05771765299755502</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.538630989961417e-13</v>
+        <v>-2.474237153936314e-11</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-3.927994469054384e-12</v>
+        <v>-9.143353970414591e-12</v>
       </c>
       <c r="BH2" t="n">
-        <v>-2.06710782267789e-12</v>
+        <v>-6.457043025080289e-11</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.004104017816115275</v>
+        <v>0.04270155257931549</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.002855286054770521</v>
+        <v>0.09202001931949719</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.00492651557234646</v>
+        <v>0.09901643485058489</v>
       </c>
       <c r="BR2" t="n">
         <v>-0</v>
@@ -1215,22 +1215,22 @@
         <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.005693211664433453</v>
+        <v>0.03131473306537002</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.009358997687507985</v>
+        <v>0.01459762577657865</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.00582859348786632</v>
+        <v>-0.1729798517821131</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.001500300432440068</v>
+        <v>-0.003602566097770099</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
@@ -1254,25 +1254,25 @@
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.003002905835919542</v>
+        <v>-0.06499494447921603</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.009959025390784405</v>
+        <v>0.09398305442539082</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01121104202471472</v>
+        <v>0.0096944815147255</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
@@ -1281,10 +1281,10 @@
         <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01115898982592852</v>
+        <v>0.01807962320476416</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.004069802801733725</v>
+        <v>0.06174616424656126</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1293,13 +1293,13 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.0001919868983490178</v>
+        <v>-0.02546861906290959</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.002867918245647163</v>
+        <v>-0.06299321675325247</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.01265176463171679</v>
+        <v>0.07641384830809356</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.002096660490765005</v>
+        <v>-0.02487358087435496</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02909157672016289</v>
+        <v>-0.03088654146854186</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.001896109504836438</v>
+        <v>0.0188745763579547</v>
       </c>
       <c r="DK2" t="n">
         <v>0</v>
@@ -1347,13 +1347,13 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.004404430582691765</v>
+        <v>-0.009637918379597099</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.01896974970946328</v>
+        <v>0.06245318978516026</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.002554970690957684</v>
+        <v>0.1467824348050349</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.01095980270414279</v>
+        <v>0.05022727504449036</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.00870369602860342</v>
+        <v>-0.03733691050958865</v>
       </c>
       <c r="EB2" t="n">
-        <v>-2.91708670990509e-05</v>
+        <v>0.07470033226465035</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.001620333304184715</v>
+        <v>-0.04922191010695148</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
@@ -1416,43 +1416,43 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01173213826752615</v>
+        <v>-0.08032838204571337</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01474483910185917</v>
+        <v>-0.01828370491640607</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.003200501373574301</v>
+        <v>-0.01887613455754341</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.007169983141607374</v>
+        <v>-0.02917418516160518</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.005763615600106384</v>
+        <v>0.03146957143655391</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.002371727097083911</v>
+        <v>-0.02839358258241504</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.004569642517073692</v>
+        <v>-0.08351880619030068</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0116744398651462</v>
+        <v>0.07422642120112805</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.001385504764308432</v>
+        <v>0.06665416958547919</v>
       </c>
       <c r="FI2" t="n">
         <v>0</v>
@@ -1497,37 +1497,37 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01185691809469933</v>
+        <v>0.09787128667257147</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0.007066085375915804</v>
+        <v>-0.02810334017930428</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01036877029110401</v>
+        <v>-0.06567877600537853</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.004004914652236327</v>
+        <v>-0.2198168691125809</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0.001401383214709259</v>
+        <v>-0.0004938037694150352</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
@@ -1539,22 +1539,22 @@
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.004921061273421835</v>
+        <v>-0.01277008084115426</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.003112587048578503</v>
+        <v>0.03328915369180503</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
@@ -1563,27 +1563,27 @@
         <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01272869644245984</v>
+        <v>0.04431246292278092</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02825232856015674</v>
+        <v>0.05151775026226867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01238054000364206</v>
+        <v>-0.006470662995368773</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1592,58 +1592,58 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04760988357058388</v>
+        <v>0.1812693029531684</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01675448567479594</v>
+        <v>-0.06393810422196199</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03111729087357156</v>
+        <v>-0.003422239117422899</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004629327165711065</v>
+        <v>0.008518432193015915</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.003651067528704101</v>
+        <v>-0.001719139641541715</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.996420201576533e-11</v>
+        <v>8.918327557329031e-12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>-0</v>
@@ -1652,43 +1652,43 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.01429011182982658</v>
+        <v>0.009352168735560051</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005450632899461022</v>
+        <v>0.09595363854509616</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.007653948883459434</v>
+        <v>-0.08483100182501815</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.001492545811534184</v>
+        <v>-0.0815624281897309</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.04094792879461371</v>
+        <v>0.01205725748139367</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.01667484003365467</v>
+        <v>-0.1305965759290494</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.09555205795994062</v>
+        <v>-0.1775428689932977</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.04851076601857499</v>
+        <v>0.09459480914303323</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.09129961054473484</v>
+        <v>0.00919407949908232</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -1724,25 +1724,25 @@
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.02383338746556338</v>
+        <v>0.02152064761019793</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001815710993722522</v>
+        <v>-0.002261671662105771</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.213160111507078e-11</v>
+        <v>-2.16566190685652e-11</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
         <v>-0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.07211537447836792</v>
+        <v>0.03873221923284528</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.02282274020874531</v>
+        <v>0.03598084052356306</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.06292966952173933</v>
+        <v>0.02850917328128756</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
@@ -1787,19 +1787,19 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.03254349279818169</v>
+        <v>-0.1377672140082567</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.001491636849612979</v>
+        <v>0.05778666328556872</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.04154624750815422</v>
+        <v>-0.03070548989790387</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
@@ -1808,22 +1808,22 @@
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.008497826624778096</v>
+        <v>0.09944209921433761</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.01111788522847863</v>
+        <v>-0.06303176925795075</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01359628398808561</v>
+        <v>-0.009230237386698932</v>
       </c>
       <c r="CI3" t="n">
         <v>-0</v>
@@ -1832,61 +1832,61 @@
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.01163394081674679</v>
+        <v>0.1007200116480376</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.04012403386809808</v>
+        <v>-0.03394987076941023</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1610210170541966</v>
+        <v>0.0481520144952328</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
         <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.02444854731209059</v>
+        <v>0.1069979293912589</v>
       </c>
       <c r="CX3" t="n">
         <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.01470688523132525</v>
+        <v>-0.07212227854296062</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.002825019366043531</v>
+        <v>-0.007427357887790766</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,16 +1895,16 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.003025560309927874</v>
+        <v>0.1499190628845912</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.002819592983963276</v>
+        <v>-0.02405692781479026</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0302903824962202</v>
+        <v>0.007347891590682306</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
@@ -1916,25 +1916,25 @@
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01164329787221335</v>
+        <v>0.03236154555124589</v>
       </c>
       <c r="DP3" t="n">
         <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.04635519912517706</v>
+        <v>-0.03932639821681442</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01488828877500927</v>
+        <v>0.01315813046524708</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1946,28 +1946,28 @@
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.02143046482714245</v>
+        <v>0.05111638949812912</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.01847054645001312</v>
+        <v>-0.002847304399068707</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.04206843145711176</v>
+        <v>-0.0003914130589379586</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
         <v>0</v>
@@ -1976,49 +1976,49 @@
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.004015754411268672</v>
+        <v>0.09741350439242748</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.009315034117417523</v>
+        <v>-0.07320613794402597</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.05194172471889759</v>
+        <v>-0.02326193504266087</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.03135857007739255</v>
+        <v>0.07050894019840914</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.02796644684578234</v>
+        <v>-0.03442667009972968</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01440381691648679</v>
+        <v>0.01958964884092233</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
@@ -2030,19 +2030,19 @@
         <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.02122078909257879</v>
+        <v>0.105853013757009</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0.007101619432497893</v>
+        <v>-0.07121869722897814</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02007375172656988</v>
+        <v>-0.0007918045017203058</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2054,19 +2054,19 @@
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.01121403535655598</v>
+        <v>-0.0275122443914001</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0.03888245854305108</v>
+        <v>-0.04386309312006665</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.01595243774510828</v>
+        <v>-0.01146356491416903</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
@@ -2075,61 +2075,61 @@
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.05076548797108247</v>
+        <v>0.1398109573198667</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.03753587515874197</v>
+        <v>0.08421420340754192</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.08575564121868826</v>
+        <v>0.04038123254141592</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.03281846210943749</v>
+        <v>0.1122873305930857</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.002460567972209788</v>
+        <v>-0.03167708412458878</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03211432155177909</v>
+        <v>0.0381028896018309</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01865813242713158</v>
+        <v>-0.004150060020444287</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01231835636767514</v>
+        <v>0.008142846053437944</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01176671555696468</v>
+        <v>-0.0360035995094681</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.002490150035315973</v>
+        <v>0.008782354460828161</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2185,52 +2185,52 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04092925448612005</v>
+        <v>0.0115774118787762</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007381841763497745</v>
+        <v>-0.002609301675192842</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0003469583873311182</v>
+        <v>-0.003936290543769455</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.00124542614912094</v>
+        <v>0.002061387310328518</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01643087795462955</v>
+        <v>-0.01659006365219288</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.022666632376176</v>
+        <v>-0.0195763343510953</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2239,16 +2239,16 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01829268116173023</v>
+        <v>0.002896009476765685</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01523656308516804</v>
+        <v>0.03203742899334518</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,37 +2257,37 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01462592904099051</v>
+        <v>-0.0006804897529636546</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.01248065732713575</v>
+        <v>-0.0198016476864264</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1185750361624378</v>
+        <v>0.1178556096180219</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.07992161887646369</v>
+        <v>-0.006765759070894674</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,13 +2296,13 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.001412597894769314</v>
+        <v>0.00482064854930216</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.003174512130097024</v>
+        <v>-0.00076597519299809</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,25 +2311,25 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.001687941472095171</v>
+        <v>-0.002346190298834312</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.02922089081445605</v>
+        <v>0.02986656678893958</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.003844187013604827</v>
+        <v>0.01666366685996415</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
@@ -2338,61 +2338,61 @@
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.05373535858483756</v>
+        <v>0.05058741686995014</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.02680998222319885</v>
+        <v>0.0136458693484807</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04946166235445827</v>
+        <v>0.06517332630243286</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0254053201292953</v>
+        <v>-0.01840869757592748</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01666292683843574</v>
+        <v>-0.0245717596355996</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.0133229341161836</v>
+        <v>-0.03079654139791788</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.009577273529854479</v>
+        <v>-0.004608475318565224</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
@@ -2404,22 +2404,22 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.01869209772149522</v>
+        <v>0.01324001538743747</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.00366367113829173</v>
+        <v>-0.04613732698496126</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002423132296382514</v>
+        <v>-0.002273061389203045</v>
       </c>
       <c r="CR4" t="n">
         <v>-0</v>
@@ -2431,13 +2431,13 @@
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.005766809980660703</v>
+        <v>0.03724234270226592</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01149886050931</v>
+        <v>-0.0305819948192732</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.006222718972896313</v>
+        <v>-0.005715748696935025</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
@@ -2458,22 +2458,22 @@
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.02019832206340788</v>
+        <v>0.01201789563098089</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.03057067236397179</v>
+        <v>-0.01868427729491209</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03726644162781242</v>
+        <v>-0.02668543635369463</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2482,133 +2482,133 @@
         <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0.01143107002990708</v>
+        <v>-0.001806153896667132</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.002173610500390051</v>
+        <v>-0.01849002380786375</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001392506838568294</v>
+        <v>-0.001447391008528046</v>
       </c>
       <c r="DS4" t="n">
         <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0.01396591242454905</v>
+        <v>-0.007225003542604202</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.008709287338219976</v>
+        <v>0.02569566268425313</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
         <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002609753144991111</v>
+        <v>0.00847861596458996</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0.01049949554763543</v>
+        <v>-0.004462234997921604</v>
       </c>
       <c r="EF4" t="n">
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.003426290485811819</v>
+        <v>-0.02450542134170786</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003929569453855625</v>
+        <v>-0.01250380993229195</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.02560942234773207</v>
+        <v>0.00624169212285732</v>
       </c>
       <c r="EO4" t="n">
         <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.04543417593317097</v>
+        <v>0.004180348430712513</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.002577728451845476</v>
+        <v>-0.003481109820141619</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.01663892712440147</v>
+        <v>-0.01834797407575164</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01965251143628528</v>
+        <v>-0.03524130719175043</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.004659769495664184</v>
+        <v>-0.01571805855221821</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
@@ -2620,70 +2620,70 @@
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.01415808208996762</v>
+        <v>0.01419841737175076</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.005866773648910276</v>
+        <v>-0.02352257330033291</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01091697616682245</v>
+        <v>0.005473194431046926</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.01337167971442908</v>
+        <v>0.04588875291313237</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.03766043872364955</v>
+        <v>0.009693092435077266</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.03060206033006855</v>
+        <v>-0.006481319217134946</v>
       </c>
       <c r="FU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0008150762667368274</v>
+        <v>0.002201334663556517</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.03594518750750733</v>
+        <v>-0.01499815241025409</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.004320773574622363</v>
+        <v>0.01713947296947874</v>
       </c>
     </row>
     <row r="5">
@@ -3278,16 +3278,16 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3074164942345954</v>
+        <v>0.1414960270647595</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09341493104617134</v>
+        <v>-0.07912334296997466</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004674670239064709</v>
+        <v>0.04392051698608722</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3305,16 +3305,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07542117018312261</v>
+        <v>-0.05653795743572259</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1341869912615439</v>
+        <v>0.157250384799392</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01291851266193206</v>
+        <v>-0.01988554094631119</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3332,16 +3332,16 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02233220189895401</v>
+        <v>0.01833950950558755</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.02742237103706371</v>
+        <v>-0.0008690580043371832</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.02538271151421819</v>
+        <v>0.0004663596391663828</v>
       </c>
       <c r="X6" t="n">
         <v>-0</v>
@@ -3350,7 +3350,7 @@
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3359,25 +3359,25 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07611775469051614</v>
+        <v>0.03562883041053132</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003225467932423122</v>
+        <v>-0.05972180522787789</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07491411140070604</v>
+        <v>-0.0661824620073363</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3386,16 +3386,16 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.07628572389906658</v>
+        <v>0.1175081303150854</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.09223501850750063</v>
+        <v>-0.08704086912696798</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.08544536949717943</v>
+        <v>0.1126132160725783</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3404,25 +3404,25 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.5317713854999866</v>
+        <v>0.2353262528321284</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.06513743244709896</v>
+        <v>-0.1895791068871116</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2342374762156317</v>
+        <v>-0.01631906981220587</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
@@ -3431,25 +3431,25 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0005167597096400455</v>
+        <v>-0.006560919618508471</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.007075147866563221</v>
+        <v>0.002299238328933677</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02636139528553031</v>
+        <v>-0.001153113856844104</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3464,25 +3464,25 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02169172162740427</v>
+        <v>-0.00803097526687558</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.06014520328497108</v>
+        <v>0.02648330547754086</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1345272154303411</v>
+        <v>0.01236800269994951</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,25 +3494,25 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.3325617574459699</v>
+        <v>0.1958753814010668</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.1176913149945369</v>
+        <v>-0.1887726820463456</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01533143797405323</v>
+        <v>0.06577074412765238</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -3521,184 +3521,184 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1161711595516032</v>
+        <v>-0.09773312169269599</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.02635387389107502</v>
+        <v>0.1415719178012855</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.04286601132051968</v>
+        <v>-0.07272048149726645</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.07074041989946581</v>
+        <v>-0.1209733557745777</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1285288398437327</v>
+        <v>0.1674504337233746</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.2113171528632981</v>
+        <v>-0.04590918509386394</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1069017878704253</v>
+        <v>-0.1043283530458304</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.06426346394443246</v>
+        <v>0.1377859312934736</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0006521649069493775</v>
+        <v>-0.06305820235762737</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01600797801108925</v>
+        <v>-0.01392048284514542</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.07389782302542051</v>
+        <v>0.05503270134856747</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09221635158958501</v>
+        <v>-0.09306510171846286</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.1090411329093383</v>
+        <v>-0.06009769440958217</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.05682610736348229</v>
+        <v>0.06651887647027838</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.04692753836719188</v>
+        <v>-0.07804710610909552</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.007025311030457646</v>
+        <v>0.05750069604741034</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.07654994292295714</v>
+        <v>0.06423980150635461</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.008867357682909941</v>
+        <v>-0.004543857971703712</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.04668066978820579</v>
+        <v>-0.03271074276959516</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.02693956084076526</v>
+        <v>0.1249024683205028</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.007347152479384608</v>
+        <v>-0.01953457484004867</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,28 +3707,28 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1379833513535925</v>
+        <v>-0.0564762082548255</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.06659283803671988</v>
+        <v>-0.0982444667433056</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.06569717950100426</v>
+        <v>-0.05832805505630705</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>-0</v>
@@ -3737,43 +3737,43 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1148811206685352</v>
+        <v>-0.1142845666609911</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.05831501288991423</v>
+        <v>0.1592639138594289</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.03244037376378027</v>
+        <v>-0.0724408383840824</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02588869626331234</v>
+        <v>-0.0446555732161408</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.06749980048397024</v>
+        <v>0.03991745154643635</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.07641861895000003</v>
+        <v>-0.04953970219654871</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
@@ -3785,25 +3785,25 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.06795110494189902</v>
+        <v>0.05342879286387819</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.01151451866390557</v>
+        <v>0.1513870292300104</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.08164723067236963</v>
+        <v>-0.0361011939864128</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3815,31 +3815,31 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.04764262769462411</v>
+        <v>-0.06928362259279111</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.02385462491590652</v>
+        <v>0.09309668778643145</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1949238575876912</v>
+        <v>0.1072395286946042</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03114498496360391</v>
+        <v>-0.03168900356202093</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07923089661822807</v>
+        <v>-0.01496754024724825</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.009342831864621334</v>
+        <v>-0.009431737799738079</v>
       </c>
       <c r="I7" t="n">
         <v>-0</v>
@@ -3874,16 +3874,16 @@
         <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01877851228479292</v>
+        <v>-0.01360906484754425</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0747743588337446</v>
+        <v>0.09253207225981802</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03751621453021287</v>
+        <v>0.0115524982683994</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.002876843763223824</v>
+        <v>-0.006322188128525858</v>
       </c>
       <c r="R7" t="n">
         <v>-0</v>
@@ -3901,25 +3901,25 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06369757708807695</v>
+        <v>0.02577509072222274</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.02272747532779318</v>
+        <v>-0.01733098268254574</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0077105335090246</v>
+        <v>-0.02411596860251135</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01745469756105694</v>
+        <v>0.00139406744934165</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3928,16 +3928,16 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01090949819782506</v>
+        <v>-0.01517457248200579</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1010786336125553</v>
+        <v>-0.05964746947648717</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01867316016433635</v>
+        <v>-0.06881670514923439</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>-0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0161259627619541</v>
+        <v>0.01196308507819079</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3955,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02574990305549862</v>
+        <v>0.07107359753692777</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.04601608618033447</v>
+        <v>-0.02017298904447758</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0719721900404449</v>
+        <v>0.02671058622569352</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,34 +3973,34 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.004297196984433509</v>
+        <v>-0.01810499534677105</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3356390603101935</v>
+        <v>0.165280831362862</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0625796232022424</v>
+        <v>-0.04945215587781198</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1362480754090794</v>
+        <v>-0.1029928454835915</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.07871231897097564</v>
+        <v>-0.02515801134476349</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.002768513706732676</v>
+        <v>8.583746412701549e-05</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.02133969973055314</v>
+        <v>-0.01335927854351663</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.08180121658650671</v>
+        <v>-0.0002710899817438778</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,34 +4027,34 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.03509336970279404</v>
+        <v>-0.02574457674511852</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.06536543766221746</v>
+        <v>0.0302522182413181</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.145763656455779</v>
+        <v>0.02299502637066579</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.06541113298625141</v>
+        <v>0.0400397581372832</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.05418167695910962</v>
+        <v>0.0142887395482432</v>
       </c>
       <c r="BT7" t="n">
         <v>-0</v>
@@ -4063,52 +4063,52 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2154047004834228</v>
+        <v>0.122187946917631</v>
       </c>
       <c r="BW7" t="n">
         <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02998234752580764</v>
+        <v>-0.04831869246606465</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01077114859756164</v>
+        <v>-0.06897986890340903</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.008820068710335936</v>
+        <v>-0.02886945781111605</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.08129824093831874</v>
+        <v>-0.05911018555116305</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01573675010557837</v>
+        <v>0.0496550855056044</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001257268742177206</v>
+        <v>0.006103011278659406</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.007887318591604405</v>
+        <v>-0.00839725602904464</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
@@ -4117,79 +4117,79 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.002549597064313447</v>
+        <v>-0.05883253653066661</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.09342829691870316</v>
+        <v>0.07558121967792708</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0546662775309722</v>
+        <v>0.08311953290442954</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0858680542764296</v>
+        <v>0.004512708312291606</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.06861693394474833</v>
+        <v>-0.06387892380652634</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04630019861552669</v>
+        <v>0.05625699777848542</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01231364008170116</v>
+        <v>0.01593005113739449</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.003515115668967814</v>
+        <v>-0.01041952672222521</v>
       </c>
       <c r="DD7" t="n">
         <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.09632281738589744</v>
+        <v>-0.05449884230304104</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.02395397350912493</v>
+        <v>0.01786519093876596</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.00298207506782805</v>
+        <v>-0.01024099851683625</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.01506645766739277</v>
+        <v>-0.009610324867367378</v>
       </c>
       <c r="DM7" t="n">
         <v>0</v>
@@ -4198,70 +4198,70 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.09020795120060893</v>
+        <v>-0.0546698146712816</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.01727420716382665</v>
+        <v>0.02690154096647007</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0427616801964659</v>
+        <v>-0.03659541033108255</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.01741933451503766</v>
+        <v>0.05251919699395777</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01224083173076354</v>
+        <v>0.0779717493669249</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.01997760123415561</v>
+        <v>0.07068641127272811</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.03689832681047959</v>
+        <v>-0.01469925141926225</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.004340778207563172</v>
+        <v>0.06975810836959316</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0474184155616106</v>
+        <v>-0.02506439015373767</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.003960614864994568</v>
+        <v>0.03079490682097445</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01948045868174289</v>
+        <v>-0.0004248506139098287</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,7 +4270,7 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.06985241617754509</v>
+        <v>-0.0205598673381537</v>
       </c>
       <c r="EN7" t="n">
         <v>0</v>
@@ -4279,133 +4279,133 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08341025629410045</v>
+        <v>0.0005122738480894703</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0554721187709872</v>
+        <v>0.03223335469896229</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.08281562392342953</v>
+        <v>-0.001458230687084032</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0.01364673971126911</v>
+        <v>-0.02037543079088083</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.07076804765967479</v>
+        <v>-0.0748812772511674</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03345761796252057</v>
+        <v>0.06019954387864247</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.008552491990315948</v>
+        <v>0.004185049641637444</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0009320875651520778</v>
+        <v>-0.009626398056018764</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02254343497725734</v>
+        <v>-0.008069265576743964</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.06511188971024752</v>
+        <v>0.009934364532437389</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.08352713753049504</v>
+        <v>0.03188138723238729</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0.005842281054725282</v>
+        <v>0.004950176817120284</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.1207536911506798</v>
+        <v>0.009535809200977872</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.05964047506557543</v>
+        <v>0.0986023914307419</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.09674116651613587</v>
+        <v>-0.106747129167537</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0.006983542009405877</v>
+        <v>0.02532910559419197</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02240828190059849</v>
+        <v>-0.03795905137337083</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.04036786999475693</v>
+        <v>0.005674394286438405</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.02228775736387072</v>
+        <v>-0.01231651231870081</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,25 +4416,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02527182781634258</v>
+        <v>0.2910626223927827</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005103148531812541</v>
+        <v>0.05798164559513822</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03645942080786833</v>
+        <v>-0.1989782815463915</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0004942887352872031</v>
+        <v>-0.00971723088152952</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002734587728454436</v>
+        <v>0.002942829023919886</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009321055219299492</v>
+        <v>0.05963207462015739</v>
       </c>
       <c r="P8" t="n">
         <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.009311291959372336</v>
+        <v>0.1025252091083143</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,52 +4479,52 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.001707484555018416</v>
+        <v>-0.05199460581044359</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003390583600845882</v>
+        <v>-2.149669444052214e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01221316796922605</v>
+        <v>-0.09930454182506944</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01781000755768598</v>
+        <v>-0.2320220937982311</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001339823274388302</v>
+        <v>0.1021058953423038</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001834663845924749</v>
+        <v>0.119796472172972</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -4533,43 +4533,43 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.00887673943388689</v>
+        <v>0.0599281607620195</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.0062577994922707</v>
+        <v>-0.03291281198581725</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.04171305763163554</v>
+        <v>0.3167514026932489</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01481848845429409</v>
+        <v>-0.2061978898147576</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.007101885675776443</v>
+        <v>-0.08475579050014669</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,52 +4578,52 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.007083798773765775</v>
+        <v>0.04642948264657372</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.006662519829755887</v>
+        <v>0.01104917860106639</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.02076713732021096</v>
+        <v>-0.0733725551768336</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0325128744668122</v>
+        <v>-0.00386585111340135</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.008043236239876747</v>
+        <v>0.09954458245562969</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.003250167010372724</v>
+        <v>0.12201060492344</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01299866386736707</v>
+        <v>0.341062570742786</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,94 +4641,94 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0006467004295372201</v>
+        <v>0.02555406704146935</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.005270244602268396</v>
+        <v>-0.1307984136902994</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.001337095902199276</v>
+        <v>-0.1528095292310003</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.00464611600510487</v>
+        <v>-0.06358954118111437</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01685776153972063</v>
+        <v>0.1294428623567939</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.004079293048314576</v>
+        <v>-0.1161354186231855</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00999404660924226</v>
+        <v>0.04210110983911319</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.01510548099276317</v>
+        <v>0.04351250234218767</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.001905780870976901</v>
+        <v>-0.1381845979850248</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0004267751575013701</v>
+        <v>-0.03530756156304545</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01491322002238111</v>
+        <v>0.1410405060745226</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>0</v>
@@ -4737,82 +4737,82 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.00419493575303595</v>
+        <v>-0.1575126150434193</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01042563186418663</v>
+        <v>-0.1579448757287264</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01189505640312133</v>
+        <v>0.1309629277939304</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.001786912834538432</v>
+        <v>-0.0916471566097804</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01004271449431568</v>
+        <v>0.03610914518366896</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.009004453197220187</v>
+        <v>0.0658489588510716</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.0133584167880645</v>
+        <v>-0.01711335921459019</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01534191556655579</v>
+        <v>0.03673013196624247</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.007329903017803468</v>
+        <v>0.1524424825830215</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,34 +4821,34 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.0001142359007693035</v>
+        <v>-0.0231432106503556</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.005969661170169345</v>
+        <v>-0.08088337950540819</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01124121991541926</v>
+        <v>0.02212098505243623</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.003940011516657378</v>
+        <v>-0.07616978308638499</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
@@ -4857,16 +4857,16 @@
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.001071998945759593</v>
+        <v>-0.2531767656425268</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.02417692945130313</v>
+        <v>0.1206578146853547</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>-0</v>
@@ -4875,19 +4875,19 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.00400579663910141</v>
+        <v>-0.1580864904076252</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.001733270420803214</v>
+        <v>-0.08642214210592236</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.01683109116464705</v>
+        <v>0.1104247803548835</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
@@ -4899,10 +4899,10 @@
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.002584715287659414</v>
+        <v>-0.2022794436790029</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02178602106301987</v>
+        <v>0.09047803132732921</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.004007797275748915</v>
+        <v>0.1793729261081488</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.002381027121123677</v>
+        <v>0.026891739177902</v>
       </c>
       <c r="FR8" t="n">
         <v>0</v>
@@ -4938,28 +4938,28 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.003152508077921613</v>
+        <v>-0.01514297568876039</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.01683238647885475</v>
+        <v>-0.06904486738799989</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02017105374383327</v>
+        <v>-0.01487674175834094</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,13 +4968,13 @@
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.001920558501812165</v>
+        <v>0.1482551055518672</v>
       </c>
       <c r="GE8" t="n">
         <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,43 +4985,43 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.179057703084732</v>
+        <v>0.1941238973989291</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05558065897604197</v>
+        <v>-0.0950865342148742</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04059605509819462</v>
+        <v>0.006534073778643351</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006646660010186468</v>
+        <v>0.01123082079384075</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04201315394694989</v>
+        <v>0.08415203990158389</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001047150342291244</v>
+        <v>0.0004840704105787979</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0404070191828752</v>
+        <v>0.05084037674339983</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.002387053340851812</v>
+        <v>-0.0107031639990193</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01594048126486085</v>
+        <v>-0.008615842017183342</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03685754622237068</v>
+        <v>-0.02999288658999665</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01107381203883821</v>
+        <v>-0.08602016747375532</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.003782447993483443</v>
+        <v>-0.07270605576228195</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.02172785289946226</v>
+        <v>0.09432652962385413</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03545205452821976</v>
+        <v>-0.08168020350064735</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04302159777676151</v>
+        <v>0.08028761204749094</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,34 +5111,34 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2703417742115063</v>
+        <v>0.2251457485742342</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.02774174471132565</v>
+        <v>-0.1176452625877232</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08278432767340703</v>
+        <v>-0.08025501383021924</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002156827818627739</v>
+        <v>-0.007375332569566909</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.02178526599238468</v>
+        <v>0.004508644823401051</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.04605738949829271</v>
+        <v>0.006119029516983383</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04954388051248602</v>
+        <v>-0.02184194180800378</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.03465274244737051</v>
+        <v>0.04598090187502039</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0868669161088883</v>
+        <v>0.06982872890887586</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1641965637135762</v>
+        <v>0.2179555366326615</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.004276743072890333</v>
+        <v>-0.1071712503250873</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02172081530906695</v>
+        <v>0.00119733655486428</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -5228,46 +5228,46 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05209855873719033</v>
+        <v>-0.09736499662727252</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001196112744174317</v>
+        <v>0.1009749326642174</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01061292794628031</v>
+        <v>-0.0200915781013824</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.02143532233217262</v>
+        <v>-0.08229470428777211</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.08323489486145619</v>
+        <v>0.09934767765722201</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1060004608147263</v>
+        <v>-0.008797920964068335</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5282,16 +5282,16 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03671194135407171</v>
+        <v>-0.1034097716900264</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.01344640472267873</v>
+        <v>0.09999930275814681</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.005658107358652037</v>
+        <v>-0.005563322143408265</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5300,31 +5300,31 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.04240421817716705</v>
+        <v>-0.09347548166262608</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.009878522023989764</v>
+        <v>0.0224076498092625</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03751443879591861</v>
+        <v>-0.0434674736504796</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,151 +5336,151 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.069047653198428</v>
+        <v>-0.07056869091737041</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.03038882862172606</v>
+        <v>0.0273249878525641</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01319929464384162</v>
+        <v>-0.0004511174178352227</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01273588766139809</v>
+        <v>0.04091841791169733</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.05076018916044874</v>
+        <v>-0.1136456560479446</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.008355395132737187</v>
+        <v>0.07748729784485563</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02952552710956375</v>
+        <v>-0.03429442879001961</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.02817614105982076</v>
+        <v>0.05927244896949802</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.01920019486426637</v>
+        <v>0.005182113630019157</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.05926352405389873</v>
+        <v>-0.05153937881968622</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.002407886373593612</v>
+        <v>0.06236339573148444</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01299695881763458</v>
+        <v>-0.03295042033414389</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.03918079164531709</v>
+        <v>-0.1151102971195147</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01779762568562731</v>
+        <v>0.1129666195653534</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.01243797696115442</v>
+        <v>-0.02564610372925147</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.03192868437423697</v>
+        <v>-0.07402411784678167</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04482164634306794</v>
+        <v>0.0261623596161783</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.005387321960322792</v>
+        <v>0.04852860280304763</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
@@ -5492,61 +5492,61 @@
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.0297976237589402</v>
+        <v>0.002909691651126213</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.01373378704100298</v>
+        <v>0.1572646422372812</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.07035325472313568</v>
+        <v>-0.01217045684827887</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.02293622947466191</v>
+        <v>-0.06442699382573974</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.04324805030302344</v>
+        <v>0.04300535990500427</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05007779304031933</v>
+        <v>0.3742250697154688</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01054906574957029</v>
+        <v>0.04084034604431774</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07564314387919324</v>
+        <v>-0.2702935281510733</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004621447042429646</v>
+        <v>0.05430932941623906</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,10 +5590,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002447002989517753</v>
+        <v>-0.004786682089348588</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006017771908539481</v>
+        <v>0.02327758437759612</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -5605,79 +5605,79 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0039141919758399</v>
+        <v>0.1108608156817956</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01993787625481741</v>
+        <v>-0.07975323100508239</v>
       </c>
       <c r="X10" t="n">
-        <v>0.003349317665797206</v>
+        <v>0.01430380015873447</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01192329041052107</v>
+        <v>-0.07191474308141836</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02306036339754872</v>
+        <v>-0.2691228356362479</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.009545907407965584</v>
+        <v>-0.05152788469718345</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01401268533857203</v>
+        <v>0.1921762484850104</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.008972330813739535</v>
+        <v>0.1437162604793143</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.017584057038823</v>
+        <v>-0.180070702316088</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,10 +5686,10 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.06188319872505958</v>
+        <v>0.4676631767615793</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,10 +5698,10 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001984766561966509</v>
+        <v>-0.2781170866130205</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.03618383507946013</v>
+        <v>-0.1896549970636888</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -5710,13 +5710,13 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01423338432031802</v>
+        <v>0.001533661373275363</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.005340084305939117</v>
+        <v>-0.08321752163187865</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.02169529952862786</v>
+        <v>-0.1553110610559389</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03706610015735281</v>
+        <v>-0.03769298728740071</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,40 +5752,40 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.00137886763856877</v>
+        <v>0.09436239037862469</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01270147721912102</v>
+        <v>0.04002123516456419</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.03098190261392727</v>
+        <v>0.3761215860448202</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.01309011307327854</v>
+        <v>-0.03378845956365425</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.008454670957304176</v>
+        <v>-0.2374664430157531</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.004026054302841274</v>
+        <v>-0.2161976336967314</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,10 +5806,10 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01439455478993529</v>
+        <v>-0.0218986712083269</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02943491584799763</v>
+        <v>0.1846736856298272</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
@@ -5818,25 +5818,25 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.002744097054387966</v>
+        <v>-0.2308361482540826</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.004421283151622923</v>
+        <v>0.3561514845284611</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.02991318706183083</v>
+        <v>0.3774211508031581</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0009843034069631272</v>
+        <v>-0.1967339121303224</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.009605319437846099</v>
+        <v>-0.01899937466407169</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.03037602462605556</v>
+        <v>0.1654223699422648</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
@@ -5878,46 +5878,46 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.005321917088333096</v>
+        <v>-0.07310574552081769</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.008656188662753677</v>
+        <v>-0.1452236996350316</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.00425153414170033</v>
+        <v>0.1057357149313698</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01368033490258256</v>
+        <v>-0.09057405113817261</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01830839338044751</v>
+        <v>-0.04148712797178136</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.001764884285027933</v>
+        <v>0.08955161996954733</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5932,34 +5932,34 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01612016922130185</v>
+        <v>0.09114174376071278</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.008038264709685964</v>
+        <v>0.005219144599889708</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0008397140750411004</v>
+        <v>0.2133290180494235</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.001335575368012285</v>
+        <v>-0.07352219945392913</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
@@ -5968,43 +5968,43 @@
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.00393921668131074</v>
+        <v>-0.0780085493044913</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0336732973658762</v>
+        <v>0.01630414059636706</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.004911591455929957</v>
+        <v>-0.113191220692946</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.02455586964675239</v>
+        <v>-0.1653656319092272</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.05776829604457789</v>
+        <v>0.09874322038805058</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
@@ -6013,19 +6013,19 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0002625791468348909</v>
+        <v>-0.2253327223515959</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01184378480620015</v>
+        <v>-0.06443365272710135</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0315454843573584</v>
+        <v>0.1536632631766075</v>
       </c>
       <c r="FD10" t="n">
         <v>-0</v>
@@ -6037,22 +6037,22 @@
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01828416510843671</v>
+        <v>-0.1674197999784489</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.00884936757940173</v>
+        <v>0.1454803514719366</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0131190577481996</v>
+        <v>-0.06347102535916738</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6067,19 +6067,19 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.001289467842618323</v>
+        <v>0.04286886152227109</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.004532772300735254</v>
+        <v>0.1364582658539795</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.005025939685359677</v>
+        <v>0.003631214738058651</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6088,13 +6088,13 @@
         <v>-0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01310175628291698</v>
+        <v>-0.06329155183341305</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6106,13 +6106,13 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.01083441456026264</v>
+        <v>0.05944752439021239</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3743193515911779</v>
+        <v>0.2146572976648557</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1005645864007494</v>
+        <v>-0.08191333418076419</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01266879395680505</v>
+        <v>-0.03359431161951782</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -6147,19 +6147,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04411592312176861</v>
+        <v>0.0393393498818256</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04058206689843002</v>
+        <v>0.04134470988795832</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.004327172684046868</v>
+        <v>-0.006530967955358893</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6174,22 +6174,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1143402732116307</v>
+        <v>0.0259282709056588</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.02776560918484423</v>
+        <v>-0.01115588452073319</v>
       </c>
       <c r="W11" t="n">
-        <v>0.003921963410133611</v>
+        <v>-0.04081702851269581</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6201,55 +6201,55 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.034030029285428</v>
+        <v>-0.01764861880314191</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01933465556032977</v>
+        <v>-0.06942409655521245</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.01951619847666063</v>
+        <v>-0.06752857508227822</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03794212496255338</v>
+        <v>0.1008190489639958</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.06838975265464836</v>
+        <v>-0.02416151814791387</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.04982647368909352</v>
+        <v>0.0615287431271252</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,25 +6258,25 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4035924967114521</v>
+        <v>0.2259287740631408</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.02170152623225912</v>
+        <v>-0.03872571992308745</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.132410953067056</v>
+        <v>-0.08866544188635678</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
@@ -6285,16 +6285,16 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0209002513132526</v>
+        <v>-0.009148405168008553</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.04228050037332897</v>
+        <v>-0.007050262708808778</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.07870231021521754</v>
+        <v>-0.01570669467983332</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,31 +6303,31 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.08771199059844108</v>
+        <v>-0.02350508178514557</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0562732221129784</v>
+        <v>0.01364466227388479</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1394501225619905</v>
+        <v>0.07281842998747963</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6339,19 +6339,19 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.249151516727693</v>
+        <v>0.1831654132859381</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.01926106791242726</v>
+        <v>-0.0859585664603108</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.05079753823878407</v>
+        <v>-0.01508115669559783</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,22 +6360,22 @@
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1042733716709371</v>
+        <v>-0.1028741096072388</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.01501755107066117</v>
+        <v>0.06529538174587507</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.02686593633488366</v>
+        <v>0.01570689257198363</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
@@ -6387,49 +6387,49 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01519892187788089</v>
+        <v>-0.07438486706161192</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.0794814897876307</v>
+        <v>0.1083643259963043</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1169072747513461</v>
+        <v>0.02296228640274509</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.09242146130369379</v>
+        <v>-0.1003298811340494</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.03190055326482938</v>
+        <v>0.06702562301730093</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.02835607320628163</v>
+        <v>0.01622653101300922</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,22 +6447,22 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.004914283446959852</v>
+        <v>0.00310113863130832</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.02703554534200887</v>
+        <v>0.01195665246314942</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0416598878403756</v>
+        <v>-0.03143690262900293</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
@@ -6474,79 +6474,79 @@
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.07829971832212836</v>
+        <v>-0.06085479572375022</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.00795865805094482</v>
+        <v>-0.01178671865193146</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.03096732837779371</v>
+        <v>-0.02043453878989292</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.03252234843670397</v>
+        <v>0.08089128014993614</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.002623193246797292</v>
+        <v>0.04326233545948036</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.07762706143819127</v>
+        <v>-0.05418601515859536</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.07493438974782489</v>
+        <v>-0.06617175788276282</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.02645106746420135</v>
+        <v>0.06528102303222631</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.008196329308332306</v>
+        <v>0.02791509622690765</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
@@ -6555,22 +6555,22 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.06940558461719064</v>
+        <v>-0.0372618322923701</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.04062240551551103</v>
+        <v>0.06099333899573915</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.03254308031319406</v>
+        <v>-0.01478461177888063</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,79 +6579,79 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.09438386436581098</v>
+        <v>-0.1069447671467327</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.02423872308956363</v>
+        <v>0.07291163416020452</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.0181587683924258</v>
+        <v>-0.0006004343891678221</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01182207684847068</v>
+        <v>-0.02915255032219688</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01663798251865446</v>
+        <v>0.01605593353988812</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03813748395499191</v>
+        <v>-0.02636615508526232</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.003291821387888793</v>
+        <v>0.01061569462804261</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0005745135726460095</v>
+        <v>0.08664216106431759</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.001949551378640368</v>
+        <v>-0.009997004314373805</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
@@ -6660,31 +6660,31 @@
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01359856473351841</v>
+        <v>-0.07915528770694846</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.04377406826714676</v>
+        <v>0.01570091858572066</v>
       </c>
       <c r="GC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4388211964457429</v>
+        <v>0.3900465227961987</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1218425185198898</v>
+        <v>-0.1523596586077099</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08540686289176971</v>
+        <v>-0.002046397806758902</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,49 +6719,49 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1243109113441424</v>
+        <v>0.1384699853312863</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05117174064583307</v>
+        <v>0.07043144781127642</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.01906684244997172</v>
+        <v>-0.006290834120117304</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1621114424947721</v>
+        <v>0.09998806240310808</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0281950731428919</v>
+        <v>-0.02880872783921848</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09436106228426988</v>
+        <v>-0.06243055417386098</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6770,52 +6770,52 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1459535117536978</v>
+        <v>-0.04340889376555832</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.04853207590519955</v>
+        <v>-0.1628585228041391</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02938176661209048</v>
+        <v>-0.04363849671124346</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07208401930385602</v>
+        <v>0.1840410316372787</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04426025404094739</v>
+        <v>-0.07613085986563313</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03557415237358803</v>
+        <v>0.1241682864778909</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6827,22 +6827,22 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.456198259663287</v>
+        <v>0.3808354809825128</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.009130371535661239</v>
+        <v>-0.1432514868567478</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1249270366666967</v>
+        <v>-0.1151008130964546</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6854,25 +6854,25 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03679241971460735</v>
+        <v>-0.03266651070698437</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.03481922215939829</v>
+        <v>-0.00783794810823729</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1416878269222811</v>
+        <v>-0.02586889300522625</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.005212196756841613</v>
+        <v>-0.01195916690963357</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05970864518148444</v>
+        <v>0.01992735009269328</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0500127714189022</v>
+        <v>0.05373284469224765</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,76 +6908,76 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3121173652447228</v>
+        <v>0.3668564677691253</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.04193154382975608</v>
+        <v>-0.1263980382942739</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.08007578505260053</v>
+        <v>-0.01338675411392098</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1207309283181497</v>
+        <v>-0.1617738327742315</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.03190375901582785</v>
+        <v>0.1438163983385437</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.03081760278052562</v>
+        <v>-0.03842395480872646</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.06417718830189151</v>
+        <v>-0.1563012303886904</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.07725371035573846</v>
+        <v>0.1834789971811151</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1932587229952875</v>
+        <v>0.02112628323876495</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1123398300874388</v>
+        <v>-0.1522221591794411</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.04521344291658282</v>
+        <v>0.1406410412448731</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02248082972006972</v>
+        <v>-0.0202457347563452</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7013,25 +7013,25 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.05678727132339498</v>
+        <v>-0.04574137701367405</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.02336023222766307</v>
+        <v>0.02141739339409299</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0002270466359257233</v>
+        <v>0.00322035966497825</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,19 +7043,19 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07910107526561207</v>
+        <v>-0.09561227061831248</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.007579799349530753</v>
+        <v>0.05623016925345568</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.09103082719173956</v>
+        <v>-0.02279043630526104</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7070,43 +7070,43 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.108106423222479</v>
+        <v>0.01378085078429292</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02855544531002914</v>
+        <v>-0.0856649259784408</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01168743399480301</v>
+        <v>0.07779956518881655</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.05609733717292423</v>
+        <v>-0.1064501442708516</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04977143995591936</v>
+        <v>0.1278886765683984</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04615442148878053</v>
+        <v>-0.003804236847012988</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,31 +7115,31 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06874145655877079</v>
+        <v>-0.113519577533804</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02854858086413556</v>
+        <v>0.07604905167041175</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0334417424932234</v>
+        <v>-0.002189646857185497</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7148,25 +7148,25 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1237033470265319</v>
+        <v>-0.178213470391958</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.05568962199300655</v>
+        <v>0.1522280169010791</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.03546435816912003</v>
+        <v>-0.04204168800204267</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,82 +7178,82 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.009153718639000209</v>
+        <v>-0.09810166670958238</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06566307982452435</v>
+        <v>0.06565346654508884</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04435073241227628</v>
+        <v>-0.01575436961684495</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01556357366105037</v>
+        <v>-0.01697281248981447</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.1691495736589476</v>
+        <v>-0.1392719008779687</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01967458937509689</v>
+        <v>-0.01148513780769735</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.06122338611806851</v>
+        <v>-0.1448031311448522</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.06025242288343506</v>
+        <v>0.08726055116937695</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7827,22 +7827,22 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.07041854567951854</v>
+        <v>0.6921540655528716</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04276080598487961</v>
+        <v>0.1615056314651589</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.03448991501585132</v>
+        <v>-0.5126915503196952</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01918446032559972</v>
+        <v>0.3435841206098446</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02016488248016724</v>
+        <v>-0.02273161357533989</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.002415639756009358</v>
+        <v>-0.04615758825648204</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -7881,37 +7881,37 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.001422112321366846</v>
+        <v>0.2011848078779573</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01512137484773312</v>
+        <v>-0.1755305513387679</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02194889142196481</v>
+        <v>-0.07755186426924385</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.02052853937479434</v>
+        <v>-0.02801959066827825</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -7920,10 +7920,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01833002718512783</v>
+        <v>-0.3663321445173358</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.008718069630720216</v>
+        <v>0.01522881440633982</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7932,13 +7932,13 @@
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01147164167603195</v>
+        <v>0.2145096923733283</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -7947,13 +7947,13 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01510961600197606</v>
+        <v>0.1018006387196487</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01086246037456286</v>
+        <v>-0.1910498032329608</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,37 +7962,37 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.05205667706959215</v>
+        <v>0.7322946677716292</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.02858743586049714</v>
+        <v>-0.2096577525104323</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.004867952513343496</v>
+        <v>-0.4284959538073818</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02874893433471825</v>
+        <v>0.02927921271735398</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,10 +8001,10 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.02180477298789317</v>
+        <v>-0.03606945434670972</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.01375656844858913</v>
+        <v>-0.1110889439839104</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
@@ -8016,28 +8016,28 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0402516855643156</v>
+        <v>0.01259220446008327</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.02494271936883833</v>
+        <v>0.1175433640258831</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01349132684054652</v>
+        <v>0.1587060623828556</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
         <v>0</v>
@@ -8046,7 +8046,7 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.03568310809729451</v>
+        <v>0.5898059517047854</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,37 +8055,37 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.009974248178150139</v>
+        <v>0.0006661211960891737</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.01441244178026927</v>
+        <v>-0.3441155475921035</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.008611055526533936</v>
+        <v>-0.2650644068612381</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.008630306697097589</v>
+        <v>-0.1002860419310075</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.009882756743934016</v>
+        <v>0.2527259674561995</v>
       </c>
       <c r="CJ14" t="n">
         <v>0</v>
@@ -8094,13 +8094,13 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.008961632045336697</v>
+        <v>-0.2874560701430511</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,10 +8109,10 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.002664999368701173</v>
+        <v>0.08083327842176372</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.0189736864903143</v>
+        <v>0.2337244479190363</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,85 +8121,85 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.004099764003274066</v>
+        <v>-0.2473403218637903</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>-0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01076196394330022</v>
+        <v>-0.07927402084578024</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.01453482255229994</v>
+        <v>0.2623917373726296</v>
       </c>
       <c r="DB14" t="n">
         <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.002708951022966143</v>
+        <v>-0.05740205177377776</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01827369814223722</v>
+        <v>-0.2766557935642747</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.002855155447541098</v>
+        <v>0.07437649051011966</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.0144376802423754</v>
+        <v>-0.08307271464959615</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.01599098606205232</v>
+        <v>-0.02126051234065438</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.01254204876073749</v>
+        <v>0.0619379040031193</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
@@ -8208,25 +8208,25 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.00306985603878843</v>
+        <v>0.03436493470233229</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.02182167655902783</v>
+        <v>0.02831508097902433</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.01877489372909164</v>
+        <v>0.1575311000024509</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
@@ -8235,52 +8235,52 @@
         <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.00135489638653182</v>
+        <v>-0.09898073604233898</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
         <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0006678494162960995</v>
+        <v>-0.1835126659985415</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.01265159192503906</v>
+        <v>0.07915393289612431</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.004246568057040912</v>
+        <v>-0.1522496242911554</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01753762879933208</v>
+        <v>-0.248271007177655</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.01420291357370249</v>
+        <v>0.2161081758086129</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
@@ -8289,19 +8289,19 @@
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.002627851761271225</v>
+        <v>-0.2776743039952409</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.008571799232864229</v>
+        <v>-0.1549054130488606</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.01632437512518428</v>
+        <v>0.2286934659457463</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01085019116500442</v>
+        <v>-0.3064263719451297</v>
       </c>
       <c r="FI14" t="n">
         <v>0</v>
@@ -8325,70 +8325,70 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03239541369999967</v>
+        <v>0.0294557153899869</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01676653891482683</v>
+        <v>0.3611431608163539</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.001858082844007534</v>
+        <v>-0.02038597567569039</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001459296042515728</v>
+        <v>-0.004359247475869218</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.002930839238697177</v>
+        <v>0.05726475444491971</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.01889523361399677</v>
+        <v>-0.09533639104674477</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.01099495732083293</v>
+        <v>0.1483703739248912</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>0</v>
@@ -8396,28 +8396,28 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.08877833924555664</v>
+        <v>0.1640533448859394</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.04446934124482185</v>
+        <v>0.01596675525644581</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01985085272268796</v>
+        <v>-0.07687368335421951</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02961278103150861</v>
+        <v>0.1055998891172665</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02116197723243367</v>
+        <v>-0.01297005204407345</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0006190800467525283</v>
+        <v>-0.00285847305163194</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,28 +8450,28 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0084893609546945</v>
+        <v>0.04599286011715191</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.009246881956212823</v>
+        <v>-0.057880745158402</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02152762153384739</v>
+        <v>0.006778515411273102</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.01975111664260675</v>
+        <v>-0.02969840739132657</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -8489,25 +8489,25 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01681542677376585</v>
+        <v>-0.07224990212691774</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.009174668573519262</v>
+        <v>-0.01222861791595267</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01455850467467693</v>
+        <v>0.04478789335574435</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
@@ -8516,16 +8516,16 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01668442175040479</v>
+        <v>-0.004802010900501488</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01265847416729718</v>
+        <v>-0.04567340542725774</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
@@ -8534,34 +8534,34 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.07345685846882351</v>
+        <v>0.1865290543804013</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.03144046500151488</v>
+        <v>-0.03977802491681733</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.001671044749558859</v>
+        <v>-0.03002485486642681</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02944109642778267</v>
+        <v>-0.004735025284202804</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,10 +8570,10 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.0268451567447865</v>
+        <v>-0.03272438552664268</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.02635909745177401</v>
+        <v>-0.06875723280410645</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8585,28 +8585,28 @@
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03480107899621444</v>
+        <v>0.02126759991328063</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.02758123969187382</v>
+        <v>0.0804588209604484</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01153581761683916</v>
+        <v>0.09041473094460561</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,61 +8615,61 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0452726762743703</v>
+        <v>0.1488897279300981</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.003064323152637533</v>
+        <v>-0.01528175869030706</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01270934978757614</v>
+        <v>-0.03848146321994624</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.01310460350038499</v>
+        <v>-0.05073450847092758</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.006331917465452871</v>
+        <v>-0.008472717131243949</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01002032160650301</v>
+        <v>0.05684274715070239</v>
       </c>
       <c r="CJ15" t="n">
         <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
       </c>
       <c r="CM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02564510775510228</v>
+        <v>-0.06266868678557422</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
@@ -8678,64 +8678,64 @@
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.002359774274639662</v>
+        <v>0.03234206209422159</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.01353445967283454</v>
+        <v>0.02139266055505797</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.008092474062298682</v>
+        <v>-0.04970774141792941</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.009807911798647864</v>
+        <v>-0.01326766186866044</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01192015604043141</v>
+        <v>0.05756126706568969</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.004981283480631214</v>
+        <v>-0.02845909671157196</v>
       </c>
       <c r="DG15" t="n">
         <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.003590181564720567</v>
+        <v>-0.01333844983609</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.001563816914731223</v>
+        <v>0.001607990276034771</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,31 +8744,31 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.005003262186655477</v>
+        <v>-0.013979992001684</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.00133529032755478</v>
+        <v>0.0005180441961292649</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.01581841308676644</v>
+        <v>-0.03773235246705126</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,19 +8777,19 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.004859067397835357</v>
+        <v>0.01236837728076392</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.03062750162122077</v>
+        <v>-0.008855181323015902</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.01807467550615735</v>
+        <v>0.03102487311926483</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8804,7 +8804,7 @@
         <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.01071583598840454</v>
+        <v>-0.02240004914058435</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
@@ -8813,64 +8813,64 @@
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.007259950332091567</v>
+        <v>-0.02734747468584777</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.002919550630913587</v>
+        <v>0.02089033865142293</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.0006664433510864164</v>
+        <v>-0.01859752307801006</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01139312301820465</v>
+        <v>-0.03566461696649732</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.01158769626503037</v>
+        <v>0.04749095044776844</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.01056723944547273</v>
+        <v>-0.04662510254550274</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.008575501604493189</v>
+        <v>-0.02977029074999938</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01384710593178252</v>
+        <v>0.03990768454882928</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
@@ -8882,10 +8882,10 @@
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01235264831950694</v>
+        <v>-0.07295995356636892</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
@@ -8894,25 +8894,25 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.0265059629771339</v>
+        <v>-0.01377170349364163</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01963442309272521</v>
+        <v>0.03620100323372234</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.004767391533324688</v>
+        <v>-0.007831728894150302</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,43 +8921,43 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0002263446708751271</v>
+        <v>-0.003178714415589739</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.004135696263798475</v>
+        <v>-0.01052734437730775</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.0249426801703967</v>
+        <v>-0.03183683790097047</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.007819773024934541</v>
+        <v>0.04163136703955109</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
@@ -9537,19 +9537,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3099996325487955</v>
+        <v>0.3496924948209171</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1520473430676675</v>
+        <v>-0.07066862840866595</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07948738901412787</v>
+        <v>0.02197810577889776</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05706306293123509</v>
+        <v>-0.1060353455375801</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9558,106 +9558,106 @@
         <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1633377197699055</v>
+        <v>0.279402406968584</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09694810127962389</v>
+        <v>-0.08290086678168367</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04905049095310452</v>
+        <v>-0.03819901420211574</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.01739968377037905</v>
+        <v>-0.01869744243328749</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06778747530504935</v>
+        <v>0.05074356883414192</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01277104845864213</v>
+        <v>-0.08112998132394891</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03801282308240116</v>
+        <v>-0.05490426138859338</v>
       </c>
       <c r="X17" t="n">
-        <v>0.05166093139754185</v>
+        <v>-0.04055783195541442</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.04645003496008007</v>
+        <v>-0.03572308210835793</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.04578744227504315</v>
+        <v>-0.1589460230143094</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.004179373705178504</v>
+        <v>-0.1104853741570418</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.006664650630156319</v>
+        <v>-0.04111754392842877</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0002630659017314988</v>
+        <v>0.1070480376558273</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.03062671145789368</v>
+        <v>-0.05575316592547826</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.04210373138906165</v>
+        <v>0.06440617187805781</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.02947037723358778</v>
+        <v>-0.0906166159573624</v>
       </c>
       <c r="AQ17" t="n">
         <v>-0</v>
@@ -9666,25 +9666,25 @@
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2941186288824618</v>
+        <v>0.2837090423896416</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.01692227407602446</v>
+        <v>-0.009640213656640983</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.04065886128373997</v>
+        <v>-0.06859510638902959</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.04399030655613984</v>
+        <v>-0.09779485629876186</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -9696,103 +9696,103 @@
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.005595269159565522</v>
+        <v>-0.004745367356232022</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.03909333742096237</v>
+        <v>-0.07403906818017626</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.09298057286533257</v>
+        <v>-0.04925628174567016</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.06281845658734803</v>
+        <v>-0.02049320995192477</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.06813108831518848</v>
+        <v>0.01170234985474954</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.06105847445403056</v>
+        <v>0.004977547382759961</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.07170751362502967</v>
+        <v>0.08326952878775615</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02145254575782661</v>
+        <v>0.01706052450878589</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1672274515514129</v>
+        <v>0.201368485997835</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.03049336237416117</v>
+        <v>-0.03952247382476279</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.01024942354970984</v>
+        <v>-0.009741511598862888</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.03791817339779943</v>
+        <v>-0.0949440537219986</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>-0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.0625915836504876</v>
+        <v>-0.1004087819739758</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0127271235749649</v>
+        <v>0.03428210223465494</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.006476174901930121</v>
+        <v>0.01302359452539014</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.03369012431948333</v>
+        <v>0.04012688801154779</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
@@ -9804,25 +9804,25 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.03064902272412317</v>
+        <v>-0.08923972831380519</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.08886404582336595</v>
+        <v>0.09328946371770591</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.07810973452156005</v>
+        <v>0.1181607260228007</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.07323239157647458</v>
+        <v>0.08661760648782897</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
         <v>-0</v>
@@ -9831,22 +9831,22 @@
         <v>0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.05085865427141057</v>
+        <v>-0.09508080942061806</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03463164200354774</v>
+        <v>0.02634718049410619</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.00521556552026968</v>
+        <v>0.011774102734365</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0431147117481105</v>
+        <v>0.0417524649315099</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9858,247 +9858,247 @@
         <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.007632717204868939</v>
+        <v>-0.03108692527340686</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0732837731701485</v>
+        <v>-0.044009824967375</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.005767680036884574</v>
+        <v>0.104861708723582</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.004554382362190317</v>
+        <v>-0.006785558575344006</v>
       </c>
       <c r="DK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01801918502989224</v>
+        <v>-0.08597538712926373</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.04399165542017191</v>
+        <v>0.03377512452335588</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0008517988928601302</v>
+        <v>-0.01232952306729009</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.01365255598983598</v>
+        <v>0.007965912965329553</v>
       </c>
       <c r="DT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="n">
         <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.01748528585245597</v>
+        <v>0.0637598246943322</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.004184540656828695</v>
+        <v>0.01180198853147689</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.03517517422446546</v>
+        <v>0.001287240228435965</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.005342607649196261</v>
+        <v>0.02633089472041544</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.08575205836553199</v>
+        <v>-0.06421736736981433</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.05425248413435411</v>
+        <v>0.04840018438457434</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.05182269844287034</v>
+        <v>0.02938821201280545</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.001135052737882999</v>
+        <v>0.0007249899937143758</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.04241188184384859</v>
+        <v>-0.02832101012125658</v>
       </c>
       <c r="EQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01322707923719843</v>
+        <v>0.01249615668341527</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.01436755760219574</v>
+        <v>0.004893719006021037</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.07622966246784686</v>
+        <v>0.08406980371917756</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.04727960417496217</v>
+        <v>-0.1103333561902732</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.01963905948037998</v>
+        <v>0.02477715930917338</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.006506999670533001</v>
+        <v>0.00569163124628621</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.03376111485827422</v>
+        <v>0.03387049482064364</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.04241331494919174</v>
+        <v>-0.03161090551720583</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.04604075009935117</v>
+        <v>0.02660974566238144</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.004987403257038624</v>
+        <v>0.003669325687421027</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.009311224950646341</v>
+        <v>0.02849530536505119</v>
       </c>
       <c r="FM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.009796780033822965</v>
+        <v>-0.09209095522433439</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.003740319932854194</v>
+        <v>0.1832580734887737</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.002628945037036377</v>
+        <v>-0.01157939304630728</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0.00118754240106085</v>
+        <v>0.1169182719667938</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
         <v>-0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.01334767892083837</v>
+        <v>-0.0957026012993525</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.03735117513608368</v>
+        <v>-0.06724594899417363</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.0127489125989381</v>
+        <v>0.008288768609014466</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10675,19 +10675,19 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2014250280682592</v>
+        <v>0.9336435119923314</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.09200631829579886</v>
+        <v>0.1891344581343335</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.08062456975761953</v>
+        <v>-0.4634319324225969</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
@@ -10702,52 +10702,52 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1169314741976602</v>
+        <v>0.9337867684822142</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05743087201827</v>
+        <v>-0.1022455774342854</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.04369611145514982</v>
+        <v>-0.2365064978490205</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.02952704333614772</v>
+        <v>0.1867991567780261</v>
       </c>
       <c r="U19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.02979583603851226</v>
+        <v>-0.08914101262550274</v>
       </c>
       <c r="X19" t="n">
-        <v>0.01735652581989239</v>
+        <v>0.06252024759630975</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>-0</v>
@@ -10756,7 +10756,7 @@
         <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.03927605968392829</v>
+        <v>0.01696330619912315</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -10765,13 +10765,13 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.02669298569573883</v>
+        <v>-0.3177397874669632</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.007339199732619318</v>
+        <v>-0.08275983957189997</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>-0</v>
@@ -10780,25 +10780,25 @@
         <v>-0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.03651967162691664</v>
+        <v>0.1967576498169837</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.01201795162506261</v>
+        <v>-0.07322698771022608</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.04574413505201786</v>
+        <v>-0.278815428178994</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
@@ -10807,37 +10807,37 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.1293526490807242</v>
+        <v>0.8106979718471371</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.03257341192550978</v>
+        <v>-0.2897166598462819</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.03328006498120321</v>
+        <v>-0.2706203243119994</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>-0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.03575674675821035</v>
+        <v>0.02284675125929471</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,70 +10846,70 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.05044775971662414</v>
+        <v>-0.086730941129772</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.01130037250511988</v>
+        <v>-0.2277943696046512</v>
       </c>
       <c r="BI19" t="n">
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.04839045177212065</v>
+        <v>0.1419268044432695</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.03335745530257225</v>
+        <v>0.1794775702816042</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.02025835431190887</v>
+        <v>0.1446443526131352</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
         <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.08692125659463283</v>
+        <v>0.6286152328161855</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.02838406756407246</v>
+        <v>-0.06768770401952547</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.003180392820273569</v>
+        <v>-0.1447493564073785</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
         <v>-0</v>
@@ -10918,7 +10918,7 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.03155980377962528</v>
+        <v>-0.2829813931652317</v>
       </c>
       <c r="CF19" t="n">
         <v>0</v>
@@ -10927,64 +10927,64 @@
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.009172091426206265</v>
+        <v>0.01362375589936514</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.01876338434070613</v>
+        <v>0.152548192445982</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.002976341298522299</v>
+        <v>-0.4636140672760531</v>
       </c>
       <c r="CO19" t="n">
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.02266085058941829</v>
+        <v>0.3291538945744021</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0.03165135832988876</v>
+        <v>0.1960929674672976</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
         <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.02430928672717448</v>
+        <v>-0.2954205202802397</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.00650877281200749</v>
+        <v>-0.06372920324723132</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.0298776638715375</v>
+        <v>0.157872271056631</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
@@ -10996,22 +10996,22 @@
         <v>0</v>
       </c>
       <c r="DE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.001680684392392846</v>
+        <v>0.01436450894135135</v>
       </c>
       <c r="DG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.02874136885777884</v>
+        <v>-0.07591485372028431</v>
       </c>
       <c r="DJ19" t="n">
-        <v>-0.001630632569430148</v>
+        <v>0.04902693049617071</v>
       </c>
       <c r="DK19" t="n">
         <v>0</v>
@@ -11020,31 +11020,31 @@
         <v>-0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.03208056501992437</v>
+        <v>-0.1863677507135232</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.03122569615192393</v>
+        <v>-0.07239628860875258</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.02934512895559011</v>
+        <v>0.1264332401981515</v>
       </c>
       <c r="DT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV19" t="n">
         <v>-0</v>
@@ -11053,19 +11053,19 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.00244316170148128</v>
+        <v>0.126444838025554</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.0330359396089983</v>
+        <v>-0.1169385883580768</v>
       </c>
       <c r="EB19" t="n">
-        <v>-0.01776810495189621</v>
+        <v>0.004610686532801153</v>
       </c>
       <c r="EC19" t="n">
         <v>-0</v>
@@ -11077,28 +11077,28 @@
         <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.01651200922167229</v>
+        <v>-0.08808270468082749</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.01804569646023286</v>
+        <v>-0.1918142533988098</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.007079115459603778</v>
+        <v>0.06845124852703949</v>
       </c>
       <c r="EL19" t="n">
         <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN19" t="n">
         <v>-0</v>
@@ -11107,34 +11107,34 @@
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.009539738808423888</v>
+        <v>-0.1179414742766615</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.007461725977477414</v>
+        <v>-0.1454742225429806</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0.03341231867210454</v>
+        <v>-0.1355047883538932</v>
       </c>
       <c r="EU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
         <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.02148890221554492</v>
+        <v>-0.3047929322790603</v>
       </c>
       <c r="EZ19" t="n">
         <v>0</v>
@@ -11143,13 +11143,13 @@
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.002581746181322266</v>
+        <v>-0.05915414286968453</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.02802274663835849</v>
+        <v>0.1272354977926765</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
@@ -11158,37 +11158,37 @@
         <v>-0</v>
       </c>
       <c r="FG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.01692005645209731</v>
+        <v>-0.2083517112023294</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.05096335375462051</v>
+        <v>0.1357175060416868</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.01434206327597235</v>
+        <v>0.1327014232268958</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.003215376394661621</v>
+        <v>-0.1509295629654764</v>
       </c>
       <c r="FR19" t="n">
         <v>-0</v>
@@ -11197,37 +11197,37 @@
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.001729138103803006</v>
+        <v>-0.0008878248848073911</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.01769520306561963</v>
+        <v>-0.05005401664657584</v>
       </c>
       <c r="FV19" t="n">
         <v>-0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>-0.02782295327691912</v>
+        <v>-0.1942478836518023</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0.02353871312291389</v>
+        <v>-0.0190101543056874</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
